--- a/Category_Hirerchy.xlsx
+++ b/Category_Hirerchy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dave_exp_manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EF9FCD1-0FE6-427C-8E6E-17E7F71A9AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5763FA35-7C77-4F70-B610-02C1EC4E3201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B2F8C96-99A0-47CC-9AAB-BB16F09FFDA9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
   <si>
     <t>Housing</t>
   </si>
@@ -183,6 +183,144 @@
   </si>
   <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>Food &amp; Drinks</t>
+  </si>
+  <si>
+    <t>Shopping</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Life &amp; Entertainment</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>Medical</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>Online Ordering</t>
+  </si>
+  <si>
+    <t>Clothes &amp; Shoes</t>
+  </si>
+  <si>
+    <t>Electronics &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Gifts</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty</t>
+  </si>
+  <si>
+    <t>Jewels &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Stationery / Tools</t>
+  </si>
+  <si>
+    <t>Home / Garden</t>
+  </si>
+  <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>Maintainance</t>
+  </si>
+  <si>
+    <t>Repairs</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Business Trips</t>
+  </si>
+  <si>
+    <t>Flights</t>
+  </si>
+  <si>
+    <t>Public Transport</t>
+  </si>
+  <si>
+    <t>Taxi</t>
+  </si>
+  <si>
+    <t>Parking</t>
+  </si>
+  <si>
+    <t>Maintainence</t>
+  </si>
+  <si>
+    <t>Spors / Fitness</t>
+  </si>
+  <si>
+    <t>Subscriptions</t>
+  </si>
+  <si>
+    <t>Cultural</t>
+  </si>
+  <si>
+    <t>Holiday / Trips / Hotels</t>
+  </si>
+  <si>
+    <t>Events / Functions</t>
+  </si>
+  <si>
+    <t>TV / Streaming</t>
+  </si>
+  <si>
+    <t>Wellness / Beauty</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Software / Apps / Games</t>
+  </si>
+  <si>
+    <t>Advisory</t>
+  </si>
+  <si>
+    <t>Fees</t>
+  </si>
+  <si>
+    <t>Fines</t>
+  </si>
+  <si>
+    <t>Charges</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Loan / Interest</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Doctor Visit</t>
+  </si>
+  <si>
+    <t>Operations / Surgery</t>
+  </si>
+  <si>
+    <t>Medicines</t>
   </si>
 </sst>
 </file>
@@ -239,68 +377,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -491,6 +587,44 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -505,20 +639,38 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3ED4042-125E-4ABC-B17C-11CCFBA14D21}" name="Table1" displayName="Table1" ref="A2:K8" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3ED4042-125E-4ABC-B17C-11CCFBA14D21}" name="Table1" displayName="Table1" ref="A2:K8" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A2:K8" xr:uid="{D3ED4042-125E-4ABC-B17C-11CCFBA14D21}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{A072B341-9FAA-4015-B996-4254279EDCDA}" name="Housing" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{35805B4B-59E4-4F60-99A9-D0D8BDA3A5B3}" name="Utilities" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{F7EA7A96-EBEE-4D82-B486-72E6D6D35FD7}" name="Food" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{7766B5D2-D0B6-488B-91E3-729AB414C26B}" name="Vehicle / Transportation" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{36578672-6F0E-40AE-9DB4-32AB9FE0435F}" name="Family" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{1FDE08F4-0919-4006-9E9B-1D36B54CB808}" name="Healthcare" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{CEED3EAD-0995-487E-9B05-092C6A7FA6E4}" name="Personal Care" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{AF8D4926-C341-4C4B-897F-8593344D0109}" name="Entertainment" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{2223E60B-8EB1-4CA5-83C4-820E3DC8C606}" name="Home" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{DC36C4D8-BD00-4715-A068-90736E2897EF}" name="Financial" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{A072B341-9FAA-4015-B996-4254279EDCDA}" name="Housing" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{35805B4B-59E4-4F60-99A9-D0D8BDA3A5B3}" name="Utilities" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{F7EA7A96-EBEE-4D82-B486-72E6D6D35FD7}" name="Food" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{7766B5D2-D0B6-488B-91E3-729AB414C26B}" name="Vehicle / Transportation" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{36578672-6F0E-40AE-9DB4-32AB9FE0435F}" name="Family" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{1FDE08F4-0919-4006-9E9B-1D36B54CB808}" name="Healthcare" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{CEED3EAD-0995-487E-9B05-092C6A7FA6E4}" name="Personal Care" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{AF8D4926-C341-4C4B-897F-8593344D0109}" name="Entertainment" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{2223E60B-8EB1-4CA5-83C4-820E3DC8C606}" name="Home" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{DC36C4D8-BD00-4715-A068-90736E2897EF}" name="Financial" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{60DD69FE-F9CE-4957-A1CE-43A2DC21B2C2}" name="Other"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{934011A8-DF7B-4896-B90A-3596C5DF585B}" name="Table2" displayName="Table2" ref="A11:I20" totalsRowShown="0">
+  <autoFilter ref="A11:I20" xr:uid="{934011A8-DF7B-4896-B90A-3596C5DF585B}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A07B3EED-D80C-47D1-94B1-E93E3071A9D4}" name="Food &amp; Drinks"/>
+    <tableColumn id="2" xr3:uid="{B77F6BE0-B42B-4E1E-A07A-18D13E64E624}" name="Shopping"/>
+    <tableColumn id="3" xr3:uid="{0D804161-5D07-4B29-96BD-28BBDB89AEC1}" name="Housing"/>
+    <tableColumn id="4" xr3:uid="{DF4C1F8E-BD78-423B-BF43-8FEB7CC76F21}" name="Transportation"/>
+    <tableColumn id="5" xr3:uid="{B3D0556D-30F7-406A-8F3B-C2E0DAB29F71}" name="Vehicle"/>
+    <tableColumn id="6" xr3:uid="{A367BD11-5234-401C-95C4-E2FF34C45671}" name="Life &amp; Entertainment"/>
+    <tableColumn id="7" xr3:uid="{AB9D56D0-23F7-4FE3-AB22-5D55C76D11C4}" name="Communication"/>
+    <tableColumn id="8" xr3:uid="{BFB7DEAC-8817-498A-BE83-770DAC8A62AD}" name="Financial"/>
+    <tableColumn id="9" xr3:uid="{13D258AE-3A44-42EF-8511-1BE011047872}" name="Medical"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -841,19 +993,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52632357-A5DF-4A5A-811E-3C870511A4DD}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -862,204 +1014,414 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="6" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>